--- a/Отчёты/0099_Отчёт.xlsx
+++ b/Отчёты/0099_Отчёт.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>713.549</t>
+          <t>785.927</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>9.172</t>
+          <t>9.056</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>211</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>397</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>541</t>
         </is>
       </c>
     </row>
@@ -564,12 +564,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>НУД ROI 5, № канала (8044.6)</t>
+          <t>НУД ROI 5, № канала (7936.8)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>790</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>0.500</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>3.289</t>
+          <t>3.288</t>
         </is>
       </c>
     </row>
@@ -672,31 +672,31 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Pn (80 кэВ)</t>
+          <t>Относительное расстояние Am241</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Отсутствует</t>
+          <t>0.110%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Pn (146 кэВ)</t>
+          <t>Fon</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Отсутствует</t>
+          <t>0.152</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Pn (400 кэВ)</t>
+          <t>Pn (80 кэВ)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Pn (850 кэВ)</t>
+          <t>Pn (146 кэВ)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -720,7 +720,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Pn (1500 кэВ)</t>
+          <t>Pn (400 кэВ)</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -732,10 +732,34 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>Pn (850 кэВ)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Отсутствует</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Pn (1500 кэВ)</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Отсутствует</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>Pn (2515 кэВ)</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Отсутствует</t>
         </is>

--- a/Отчёты/0099_Отчёт.xlsx
+++ b/Отчёты/0099_Отчёт.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>785.927</t>
+          <t>713.549</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>9.056</t>
+          <t>9.172</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>217</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>400</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>542</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>788</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.467</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>3.288</t>
+          <t>3.289</t>
         </is>
       </c>
     </row>
@@ -672,12 +672,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Относительное расстояние Am241</t>
+          <t>От Am241 до прямой</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>0.110%</t>
+          <t>0.085</t>
         </is>
       </c>
     </row>
